--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_AnhTruc_110726.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_AnhTruc_110726.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 08\01. Báo giá sửa chữa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 09\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D902AF2-B3CB-4442-9246-6D6FEA2EE666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD42289-9BAB-4B40-9685-F5C7D01F34ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -141,7 +141,7 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>Đợi phản hồi báo giá từ KD. Lực, đẩy BG sang tháng 9</t>
+    <t>KH không phản hồi, hủy báo giá trả thiết bị cho khách</t>
   </si>
 </sst>
 </file>

--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_AnhTruc_110726.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_AnhTruc_110726.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 09\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD42289-9BAB-4B40-9685-F5C7D01F34ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B818A96-903C-4C2C-A6AE-544F91FC5FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BG" sheetId="1" r:id="rId1"/>
@@ -252,15 +252,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -505,12 +505,86 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -530,81 +604,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -987,82 +987,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44"/>
-      <c r="B1" s="45"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="54" t="s">
+      <c r="A1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="56"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="51" t="s">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="53"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="40"/>
     </row>
     <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="57" t="s">
+      <c r="A3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="59"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="49"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="60" t="s">
+      <c r="A4" s="36"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="62"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="49"/>
     </row>
     <row r="5" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="40"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="18"/>
@@ -1073,11 +1073,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -1087,11 +1087,11 @@
       <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
@@ -1104,11 +1104,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
@@ -1149,7 +1149,7 @@
       <c r="J10" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="30" t="s">
+      <c r="K10" s="29" t="s">
         <v>33</v>
       </c>
       <c r="AA10" s="2"/>
@@ -1186,24 +1186,24 @@
         <f>PRODUCT(H11:I11)</f>
         <v>200000</v>
       </c>
-      <c r="K11" s="29" t="s">
+      <c r="K11" s="62" t="s">
         <v>34</v>
       </c>
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="31">
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="30">
         <f>SUM(J11:J11)</f>
         <v>200000</v>
       </c>
@@ -1237,37 +1237,37 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
       <c r="E15" s="8"/>
       <c r="F15" s="17"/>
-      <c r="G15" s="36" t="s">
+      <c r="G15" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
       <c r="E16" s="10"/>
       <c r="F16" s="15"/>
-      <c r="G16" s="37" t="s">
+      <c r="G16" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1338,20 +1338,20 @@
       <c r="AA21" s="2"/>
     </row>
     <row r="22" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
       <c r="E22" s="9"/>
       <c r="F22" s="14"/>
-      <c r="G22" s="35" t="s">
+      <c r="G22" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="59"/>
       <c r="K22" s="14"/>
       <c r="AA22" s="2"/>
     </row>
@@ -1429,16 +1429,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="17">
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A15:D15"/>
@@ -1446,6 +1436,16 @@
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="G22:J22"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="D4:J4"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <hyperlinks>
